--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>52.9102</v>
+        <v>56.7814</v>
       </c>
       <c r="E2" t="n">
-        <v>50.7374</v>
+        <v>52.8071</v>
       </c>
       <c r="F2" t="n">
-        <v>2.172399999999999</v>
+        <v>3.974100000000001</v>
       </c>
       <c r="G2" t="n">
         <v>38.1447</v>
@@ -610,13 +610,13 @@
         <v>42.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7007999999999996</v>
+        <v>3.1706</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.1934</v>
+        <v>-1.1241</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4931</v>
+        <v>4.2948</v>
       </c>
       <c r="V2" t="n">
         <v>21.3153</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>25.9361</v>
+        <v>24.8093</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4195</v>
+        <v>15.3416</v>
       </c>
       <c r="F3" t="n">
-        <v>3.516799999999999</v>
+        <v>9.4679</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.462</v>
+        <v>4.574100000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.7326</v>
+        <v>0.2812999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7293</v>
+        <v>4.2929</v>
       </c>
       <c r="J3" t="n">
-        <v>9.715100000000001</v>
+        <v>17.5564</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6854</v>
+        <v>9.849</v>
       </c>
       <c r="L3" t="n">
-        <v>2.029999999999999</v>
+        <v>7.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-18.177</v>
+        <v>-12.9822</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.4181</v>
+        <v>-9.567500000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.7592</v>
+        <v>-3.4146</v>
       </c>
       <c r="P3" t="n">
-        <v>8.3028</v>
+        <v>14.7186</v>
       </c>
       <c r="Q3" t="n">
-        <v>-30.9468</v>
+        <v>-15.096</v>
       </c>
       <c r="R3" t="n">
-        <v>39.2496</v>
+        <v>29.8146</v>
       </c>
       <c r="S3" t="n">
-        <v>10.4691</v>
+        <v>-0.7059999999999997</v>
       </c>
       <c r="T3" t="n">
-        <v>15.4837</v>
+        <v>0.1650999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.015</v>
+        <v>-0.8713000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>15.6262</v>
+        <v>6.2226</v>
       </c>
       <c r="W3" t="n">
-        <v>28.1668</v>
+        <v>12.7158</v>
       </c>
       <c r="X3" t="n">
-        <v>-12.5406</v>
+        <v>-6.493200000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24.7988</v>
+        <v>22.3598</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0649</v>
+        <v>12.1735</v>
       </c>
       <c r="F4" t="n">
-        <v>11.7338</v>
+        <v>10.1859</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.311700000000001</v>
+        <v>-8.462</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.2624</v>
+        <v>-6.7326</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9509</v>
+        <v>-1.7293</v>
       </c>
       <c r="J4" t="n">
-        <v>12.3035</v>
+        <v>9.715100000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>4.923900000000001</v>
+        <v>7.6854</v>
       </c>
       <c r="L4" t="n">
-        <v>7.379799999999999</v>
+        <v>2.029999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.615</v>
+        <v>-18.177</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.1864</v>
+        <v>-14.4181</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4285999999999999</v>
+        <v>-3.7592</v>
       </c>
       <c r="P4" t="n">
-        <v>4.1514</v>
+        <v>8.3028</v>
       </c>
       <c r="Q4" t="n">
-        <v>-17.9265</v>
+        <v>-30.9468</v>
       </c>
       <c r="R4" t="n">
-        <v>22.0779</v>
+        <v>39.2496</v>
       </c>
       <c r="S4" t="n">
-        <v>12.9252</v>
+        <v>6.8924</v>
       </c>
       <c r="T4" t="n">
-        <v>7.2744</v>
+        <v>5.2382</v>
       </c>
       <c r="U4" t="n">
-        <v>5.6511</v>
+        <v>1.6543</v>
       </c>
       <c r="V4" t="n">
-        <v>9.033799999999999</v>
+        <v>15.6262</v>
       </c>
       <c r="W4" t="n">
-        <v>11.4136</v>
+        <v>28.1668</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3798</v>
+        <v>-12.5406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>13.8754</v>
+        <v>17.1313</v>
       </c>
       <c r="E5" t="n">
-        <v>9.922000000000001</v>
+        <v>7.6673</v>
       </c>
       <c r="F5" t="n">
-        <v>3.952999999999999</v>
+        <v>9.4641</v>
       </c>
       <c r="G5" t="n">
-        <v>4.574100000000001</v>
+        <v>-1.311700000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2812999999999999</v>
+        <v>-8.2624</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2929</v>
+        <v>6.9509</v>
       </c>
       <c r="J5" t="n">
-        <v>17.5564</v>
+        <v>12.3035</v>
       </c>
       <c r="K5" t="n">
-        <v>9.849</v>
+        <v>4.923900000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>7.7075</v>
+        <v>7.379799999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.9822</v>
+        <v>-13.615</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.567500000000001</v>
+        <v>-13.1864</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.4146</v>
+        <v>-0.4285999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>14.7186</v>
+        <v>4.1514</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.096</v>
+        <v>-17.9265</v>
       </c>
       <c r="R5" t="n">
-        <v>29.8146</v>
+        <v>22.0779</v>
       </c>
       <c r="S5" t="n">
-        <v>-11.6401</v>
+        <v>5.2579</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.2541</v>
+        <v>1.8767</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.3861</v>
+        <v>3.3812</v>
       </c>
       <c r="V5" t="n">
-        <v>6.2226</v>
+        <v>9.033799999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>12.7158</v>
+        <v>11.4136</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.493200000000001</v>
+        <v>-2.3798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>7.4884</v>
+        <v>13.6275</v>
       </c>
       <c r="E6" t="n">
-        <v>7.4884</v>
+        <v>3.3037</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>10.324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4884</v>
+        <v>10.8344</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1698</v>
+        <v>1.0808</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3189</v>
+        <v>9.7538</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4884</v>
+        <v>29.6349</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1698</v>
+        <v>16.23</v>
       </c>
       <c r="L6" t="n">
-        <v>4.3189</v>
+        <v>13.4047</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-18.7999</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-15.1492</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-3.6513</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>9.057600000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-29.0598</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>38.1174</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.0331</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1.7603</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.7933</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-8.297600000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.489000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-12.7866</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6.9918</v>
+        <v>8.1091</v>
       </c>
       <c r="E7" t="n">
-        <v>7.0948</v>
+        <v>7.5822</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1032000000000001</v>
+        <v>0.5270999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>8.292</v>
@@ -1000,13 +1000,13 @@
         <v>4.340100000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0741</v>
+        <v>0.04339999999999997</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3688</v>
+        <v>0.1184</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7052</v>
+        <v>-0.07499999999999998</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6036000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0512</v>
+        <v>7.4884</v>
       </c>
       <c r="E8" t="n">
-        <v>1.481500000000001</v>
+        <v>7.4884</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5698</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6962</v>
+        <v>7.4884</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7419</v>
+        <v>3.1698</v>
       </c>
       <c r="I8" t="n">
-        <v>3.437799999999999</v>
+        <v>4.3189</v>
       </c>
       <c r="J8" t="n">
-        <v>10.1076</v>
+        <v>7.4884</v>
       </c>
       <c r="K8" t="n">
-        <v>7.8216</v>
+        <v>3.1698</v>
       </c>
       <c r="L8" t="n">
-        <v>2.286399999999999</v>
+        <v>4.3189</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.4116</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.5632</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1513</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>13.0203</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-9.057600000000001</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>22.0779</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0728</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4742999999999999</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5469</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-10.7382</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9054000000000002</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.6436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>4.953299999999999</v>
+        <v>6.3492</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1139000000000001</v>
+        <v>0.7976999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8396</v>
+        <v>5.5515</v>
       </c>
       <c r="G9" t="n">
         <v>1.9541</v>
@@ -1156,13 +1156,13 @@
         <v>16.6056</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6313</v>
+        <v>-1.2357</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2145</v>
+        <v>-1.5309</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4168000000000001</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-0.03040000000000009</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>4.0827</v>
+        <v>4.3644</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.4748</v>
+        <v>2.4188</v>
       </c>
       <c r="F10" t="n">
-        <v>22.5574</v>
+        <v>1.9458</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9376</v>
+        <v>1.6962</v>
       </c>
       <c r="H10" t="n">
-        <v>10.6821</v>
+        <v>-1.7419</v>
       </c>
       <c r="I10" t="n">
-        <v>2.255199999999999</v>
+        <v>3.437799999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>32.9871</v>
+        <v>10.1076</v>
       </c>
       <c r="K10" t="n">
-        <v>27.7533</v>
+        <v>7.8216</v>
       </c>
       <c r="L10" t="n">
-        <v>5.2338</v>
+        <v>2.286399999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-20.0493</v>
+        <v>-8.4116</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.0709</v>
+        <v>-9.5632</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.978499999999999</v>
+        <v>1.1513</v>
       </c>
       <c r="P10" t="n">
-        <v>-29.0598</v>
+        <v>13.0203</v>
       </c>
       <c r="Q10" t="n">
-        <v>-72.27209999999999</v>
+        <v>-9.057600000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>43.2123</v>
+        <v>22.0779</v>
       </c>
       <c r="S10" t="n">
-        <v>13.8506</v>
+        <v>0.3864</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5491000000000003</v>
+        <v>0.4631999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3015</v>
+        <v>-0.07669999999999993</v>
       </c>
       <c r="V10" t="n">
-        <v>6.3543</v>
+        <v>-10.7382</v>
       </c>
       <c r="W10" t="n">
-        <v>20.2608</v>
+        <v>0.9054000000000002</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.9065</v>
+        <v>-11.6436</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2278</v>
+        <v>2.1568</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1232</v>
+        <v>1.0257</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1046</v>
+        <v>1.1311</v>
       </c>
       <c r="G11" t="n">
         <v>0.8937</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4662</v>
+        <v>0.3952</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4144</v>
+        <v>0.317</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0517</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.3018</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>M. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2112</v>
+        <v>0.8779</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7666</v>
+        <v>-0.4689</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9779</v>
+        <v>1.3468</v>
       </c>
       <c r="G12" t="n">
-        <v>10.8344</v>
+        <v>0.9008</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0808</v>
+        <v>-0.3592</v>
       </c>
       <c r="I12" t="n">
-        <v>9.7538</v>
+        <v>1.26</v>
       </c>
       <c r="J12" t="n">
-        <v>29.6349</v>
+        <v>0.1542</v>
       </c>
       <c r="K12" t="n">
-        <v>16.23</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>13.4047</v>
+        <v>0.7403</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.7999</v>
+        <v>0.7466</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.1492</v>
+        <v>0.227</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.6513</v>
+        <v>0.5196</v>
       </c>
       <c r="P12" t="n">
-        <v>9.057600000000001</v>
+        <v>0.7548</v>
       </c>
       <c r="Q12" t="n">
-        <v>-29.0598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>38.1174</v>
+        <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.3832</v>
+        <v>-0.1361</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.8309</v>
+        <v>0.0185</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5523999999999998</v>
+        <v>-0.1546</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.297600000000001</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>4.489000000000001</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.7866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. JIMENA LLORCA</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5772</v>
+        <v>-0.02410000000000023</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-10.4254</v>
       </c>
       <c r="F13" t="n">
-        <v>1.241</v>
+        <v>10.401</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9008</v>
+        <v>6.3658</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3592</v>
+        <v>13.2845</v>
       </c>
       <c r="I13" t="n">
-        <v>1.26</v>
+        <v>-6.918899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1542</v>
+        <v>31.8466</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5862000000000001</v>
+        <v>31.0239</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7403</v>
+        <v>0.8224999999999995</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7466</v>
+        <v>-25.4803</v>
       </c>
       <c r="N13" t="n">
-        <v>0.227</v>
+        <v>-17.7395</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5196</v>
+        <v>-7.7411</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7548</v>
+        <v>-14.9073</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-57.5535</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7548</v>
+        <v>42.6462</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4368</v>
+        <v>-0.8702999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1764</v>
+        <v>-5.0741</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2604</v>
+        <v>4.2036</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>9.387499999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>20.3558</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-10.9683</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3376</v>
+        <v>-0.3641</v>
       </c>
       <c r="E14" t="n">
         <v>-1.497</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1593</v>
+        <v>1.133</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6154999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.4531</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.005300000000000027</v>
+        <v>-0.03170000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1118</v>
+        <v>-0.1117</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1066</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2828</v>
@@ -1579,13 +1579,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5396000000000001</v>
+        <v>-0.5130999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>-0.0518</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4876</v>
+        <v>-0.4611999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3038999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2545</v>
+        <v>-0.2281</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.07819999999999999</v>
+        <v>-0.0517</v>
       </c>
       <c r="V15" t="n">
         <v>0.019</v>
@@ -1657,13 +1657,13 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7575000000000003</v>
+        <v>-0.8292999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7535000000000003</v>
+        <v>-0.006000000000000227</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.511</v>
+        <v>-0.8231999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1146</v>
@@ -1702,13 +1702,13 @@
         <v>6.9819</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8665</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.059</v>
+        <v>1.2995</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1925</v>
+        <v>-0.5048</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018000000000001</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1011</v>
+        <v>-0.9063</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6672</v>
+        <v>-0.4724</v>
       </c>
       <c r="F17" t="n">
         <v>-0.4339</v>
@@ -1780,10 +1780,10 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4485</v>
+        <v>-0.2537</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0588</v>
+        <v>0.1361</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3897</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.093999999999999</v>
+        <v>-2.257800000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.805899999999999</v>
+        <v>-20.4586</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2878</v>
+        <v>18.2007</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1623</v>
+        <v>12.9376</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5764</v>
+        <v>10.6821</v>
       </c>
       <c r="I18" t="n">
-        <v>5.7387</v>
+        <v>2.255199999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>20.309</v>
+        <v>32.9871</v>
       </c>
       <c r="K18" t="n">
-        <v>12.2376</v>
+        <v>27.7533</v>
       </c>
       <c r="L18" t="n">
-        <v>8.0716</v>
+        <v>5.2338</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.1469</v>
+        <v>-20.0493</v>
       </c>
       <c r="N18" t="n">
-        <v>-14.814</v>
+        <v>-17.0709</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3327</v>
+        <v>-2.978499999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-20.5683</v>
+        <v>-29.0598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-42.8349</v>
+        <v>-72.27209999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>22.2666</v>
+        <v>43.2123</v>
       </c>
       <c r="S18" t="n">
-        <v>17.5838</v>
+        <v>7.5099</v>
       </c>
       <c r="T18" t="n">
-        <v>11.9106</v>
+        <v>-1.435</v>
       </c>
       <c r="U18" t="n">
-        <v>5.673100000000001</v>
+        <v>8.944699999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.2718</v>
+        <v>6.3543</v>
       </c>
       <c r="W18" t="n">
-        <v>8.809200000000001</v>
+        <v>20.2608</v>
       </c>
       <c r="X18" t="n">
-        <v>-12.0811</v>
+        <v>-13.9065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-11.5585</v>
+        <v>-11.7073</v>
       </c>
       <c r="E19" t="n">
-        <v>-22.433</v>
+        <v>-7.117100000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>10.8744</v>
+        <v>-4.5902</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3658</v>
+        <v>-9.7197</v>
       </c>
       <c r="H19" t="n">
-        <v>13.2845</v>
+        <v>-3.3439</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.918899999999999</v>
+        <v>-6.375599999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>31.8466</v>
+        <v>-4.5629</v>
       </c>
       <c r="K19" t="n">
-        <v>31.0239</v>
+        <v>-0.8709999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8224999999999995</v>
+        <v>-3.6919</v>
       </c>
       <c r="M19" t="n">
-        <v>-25.4803</v>
+        <v>-5.1571</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.7395</v>
+        <v>-2.4732</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.7411</v>
+        <v>-2.6841</v>
       </c>
       <c r="P19" t="n">
-        <v>-14.9073</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-57.5535</v>
+        <v>-2.8305</v>
       </c>
       <c r="R19" t="n">
-        <v>42.6462</v>
+        <v>3.2079</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.4049</v>
+        <v>-0.516</v>
       </c>
       <c r="T19" t="n">
-        <v>-17.082</v>
+        <v>0.2761</v>
       </c>
       <c r="U19" t="n">
-        <v>4.6771</v>
+        <v>-0.7921</v>
       </c>
       <c r="V19" t="n">
-        <v>9.387499999999999</v>
+        <v>-1.8488</v>
       </c>
       <c r="W19" t="n">
-        <v>20.3558</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-10.9683</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.2904</v>
+        <v>-11.8951</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.4092</v>
+        <v>-9.0733</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.8812</v>
+        <v>-2.8215</v>
       </c>
       <c r="G20" t="n">
-        <v>-9.7197</v>
+        <v>3.1623</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.3439</v>
+        <v>-2.5764</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.375599999999999</v>
+        <v>5.7387</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.5629</v>
+        <v>20.309</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8709999999999999</v>
+        <v>12.2376</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.6919</v>
+        <v>8.0716</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.1571</v>
+        <v>-17.1469</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4732</v>
+        <v>-14.814</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6841</v>
+        <v>-2.3327</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3774</v>
+        <v>-20.5683</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8305</v>
+        <v>-42.8349</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2079</v>
+        <v>22.2666</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0993</v>
+        <v>8.7826</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0161</v>
+        <v>4.6429</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0834</v>
+        <v>4.1395</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8488</v>
+        <v>-3.2718</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>8.809200000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8488</v>
+        <v>-12.0811</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>121.4254</v>
+        <v>135.558</v>
       </c>
       <c r="E21" t="n">
-        <v>56.42980000000001</v>
+        <v>61.0355</v>
       </c>
       <c r="F21" t="n">
-        <v>64.99530000000001</v>
+        <v>74.523</v>
       </c>
       <c r="G21" t="n">
         <v>73.8754</v>
@@ -2083,7 +2083,7 @@
         <v>-32.4918</v>
       </c>
       <c r="P21" t="n">
-        <v>-12.4542</v>
+        <v>-12.45420000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-349.095</v>
@@ -2092,16 +2092,16 @@
         <v>336.6408</v>
       </c>
       <c r="S21" t="n">
-        <v>17.1554</v>
+        <v>31.28890000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2663</v>
+        <v>3.3392</v>
       </c>
       <c r="U21" t="n">
-        <v>18.4214</v>
+        <v>27.9487</v>
       </c>
       <c r="V21" t="n">
-        <v>42.8475</v>
+        <v>42.84750000000001</v>
       </c>
       <c r="W21" t="n">
         <v>149.7718</v>
